--- a/sheets/대금율보/검수/안녕.xlsx
+++ b/sheets/대금율보/검수/안녕.xlsx
@@ -4330,19 +4330,14 @@
       </c>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="K7" s="22"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B8" s="21"/>
       <c r="C8" s="25"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
@@ -4534,11 +4529,7 @@
         </is>
       </c>
       <c r="C12" s="25"/>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D12" s="21"/>
       <c r="E12" s="25"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
@@ -4659,8 +4650,7 @@
       </c>
       <c r="F15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -4865,19 +4855,11 @@
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D20" s="21"/>
       <c r="E20" s="25"/>
       <c r="F20" s="21"/>
       <c r="G20" s="25"/>
-      <c r="H20" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H20" s="21"/>
       <c r="I20" s="25"/>
       <c r="J20" s="21" t="inlineStr">
         <is>

--- a/sheets/대금율보/검수/안녕.xlsx
+++ b/sheets/대금율보/검수/안녕.xlsx
@@ -4068,22 +4068,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="71.43" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="63.84" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="K3" s="24"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="63.84" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="K4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="63.84" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="K5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="63.84" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="K6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="63.84" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="63.84" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="25"/>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="K8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="63.84" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="K9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="63.84" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="K10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="63.84" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="63.84" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="K12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="63.84" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="K13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="63.84" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
       <c r="J14" s="21"/>
       <c r="K14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="63.84" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="63.84" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="K16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="63.84" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="K17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="63.84" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
       <c r="J18" s="21"/>
       <c r="K18" s="26"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="63.84" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="K19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="63.84" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="25"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="K20" s="25"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="63.84" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="25"/>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="K21" s="25"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="63.84" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="26"/>
@@ -4946,6 +4946,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
 </worksheet>
 </file>